--- a/tables/table2_manual.xlsx
+++ b/tables/table2_manual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lizawood/Documents/Davis/R-Projects/organicseed/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C962725F-0AD6-7941-A45C-A98829B67ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A991B11-C066-CD4E-832B-90A48D369212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="1500" windowWidth="27240" windowHeight="15940" xr2:uid="{90C725CD-3963-F942-A26A-C81268D64BF6}"/>
   </bookViews>
@@ -1096,5 +1096,6 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>